--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:31</t>
+    <t xml:space="preserve">2026-09-09 23:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:28</t>
+    <t xml:space="preserve">2026-09-17 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:23</t>
+    <t xml:space="preserve">2026-09-23 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:51</t>
+    <t xml:space="preserve">2026-10-01 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -162,7 +162,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1201,7 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:15</t>
+    <t xml:space="preserve">2026-10-02 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:23</t>
+    <t xml:space="preserve">2026-10-02 13:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Curanilahue</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Contulmo</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:55</t>
+    <t xml:space="preserve">2026-10-04 09:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:27</t>
+    <t xml:space="preserve">2026-10-05 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
